--- a/data/trans_camb/P19C07-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C07-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,16</t>
+          <t>-2,15; 2,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 1,43</t>
+          <t>-2,82; 1,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 4,39</t>
+          <t>-1,52; 4,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,97</t>
+          <t>-2,34; 1,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,44</t>
+          <t>-1,34; 3,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,92</t>
+          <t>-2,4; 1,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,67</t>
+          <t>-1,61; 1,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,89</t>
+          <t>-1,26; 1,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,51</t>
+          <t>-1,24; 2,36</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,77; 93,47</t>
+          <t>-45,81; 119,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,16; 73,08</t>
+          <t>-61,88; 68,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-37,54; 181,24</t>
+          <t>-38,25; 178,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-47,06; 78,44</t>
+          <t>-51,73; 71,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 127,77</t>
+          <t>-28,65; 120,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,35; 69,53</t>
+          <t>-48,53; 76,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,65; 62,76</t>
+          <t>-39,07; 50,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,86; 70,09</t>
+          <t>-30,97; 62,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 90,42</t>
+          <t>-30,37; 91,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,7</t>
+          <t>-3,12; 0,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,73</t>
+          <t>-2,37; 1,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,22</t>
+          <t>-4,03; 0,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,56</t>
+          <t>-0,08; 3,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,08</t>
+          <t>-1,21; 1,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,51</t>
+          <t>-0,85; 2,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,84</t>
+          <t>-0,96; 1,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,37</t>
+          <t>-1,22; 1,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,91</t>
+          <t>-1,99; 0,88</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,88; 25,59</t>
+          <t>-59,41; 32,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,46; 64,19</t>
+          <t>-47,26; 60,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-77,1; 7,18</t>
+          <t>-75,89; 8,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 175,11</t>
+          <t>-4,78; 191,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,15; 103,18</t>
+          <t>-34,64; 100,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,46; 130,87</t>
+          <t>-23,71; 134,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 69,14</t>
+          <t>-23,56; 65,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,86; 51,1</t>
+          <t>-31,88; 51,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,41; 35,63</t>
+          <t>-50,77; 32,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,54</t>
+          <t>-1,88; 2,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,93</t>
+          <t>-3,1; 0,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 4,79</t>
+          <t>-0,47; 4,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,65</t>
+          <t>-3,45; 0,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,67</t>
+          <t>-1,74; 2,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 3,21</t>
+          <t>-2,18; 3,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,93</t>
+          <t>-2,04; 1,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,44</t>
+          <t>-1,77; 1,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,24</t>
+          <t>-0,78; 3,11</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 103,58</t>
+          <t>-44,99; 112,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-69,41; 50,72</t>
+          <t>-69,43; 49,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 205,87</t>
+          <t>-14,15; 207,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-69,14; 32,1</t>
+          <t>-71,99; 21,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 114,28</t>
+          <t>-38,31; 113,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,33; 120,08</t>
+          <t>-45,09; 127,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,19; 38,67</t>
+          <t>-49,12; 41,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-39,77; 57,41</t>
+          <t>-43,18; 43,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 122,9</t>
+          <t>-17,06; 117,88</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,21</t>
+          <t>-1,32; 2,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,06</t>
+          <t>-2,27; 1,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,7</t>
+          <t>-2,67; 0,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,79</t>
+          <t>-2,1; 1,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,63</t>
+          <t>-3,03; 0,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,69</t>
+          <t>-2,06; 1,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,37</t>
+          <t>-1,26; 1,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,45</t>
+          <t>-2,14; 0,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,8</t>
+          <t>-2,02; 0,85</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,92; 105,09</t>
+          <t>-33,5; 110,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-54,77; 50,45</t>
+          <t>-55,94; 48,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,42; 33,42</t>
+          <t>-63,94; 29,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,68; 63,03</t>
+          <t>-43,17; 60,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,37; 26,07</t>
+          <t>-59,73; 25,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,97; 62,26</t>
+          <t>-42,82; 57,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,31; 46,58</t>
+          <t>-30,11; 43,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-49,57; 20,2</t>
+          <t>-50,87; 6,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,97; 26,3</t>
+          <t>-45,38; 28,71</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,94</t>
+          <t>-1,13; 0,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,42</t>
+          <t>-1,69; 0,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,92</t>
+          <t>-1,42; 0,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,11</t>
+          <t>-0,83; 1,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,13</t>
+          <t>-0,76; 1,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,36</t>
+          <t>-0,72; 1,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,75</t>
+          <t>-0,7; 0,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,48</t>
+          <t>-0,95; 0,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,88</t>
+          <t>-0,8; 0,81</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-27,19; 31,98</t>
+          <t>-28,29; 30,2</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 15,33</t>
+          <t>-41,09; 11,97</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,45; 31,48</t>
+          <t>-36,79; 31,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 37,9</t>
+          <t>-20,56; 36,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 38,23</t>
+          <t>-19,29; 34,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 44,81</t>
+          <t>-18,2; 44,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 24,27</t>
+          <t>-18,08; 24,48</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 15,79</t>
+          <t>-25,08; 16,3</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 28,23</t>
+          <t>-21,08; 26,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C07-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C07-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,23</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,29</t>
+          <t>-2,08; 2,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,39</t>
+          <t>-2,82; 1,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 4,25</t>
+          <t>-1,76; 3,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,72</t>
+          <t>-2,42; 1,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,46</t>
+          <t>-1,19; 3,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,97</t>
+          <t>-2,37; 1,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,37</t>
+          <t>-1,51; 1,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,73</t>
+          <t>-1,36; 1,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,36</t>
+          <t>-1,27; 2,05</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-2,8%</t>
+          <t>-6,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,81; 119,54</t>
+          <t>-47,7; 114,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-61,88; 68,23</t>
+          <t>-60,61; 72,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 178,39</t>
+          <t>-42,62; 138,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,73; 71,87</t>
+          <t>-49,06; 79,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 120,99</t>
+          <t>-28,39; 142,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,53; 76,28</t>
+          <t>-48,8; 80,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 50,56</t>
+          <t>-35,49; 61,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 62,83</t>
+          <t>-30,77; 70,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 91,39</t>
+          <t>-30,6; 74,01</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,85</t>
+          <t>-1,52</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-0,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,81</t>
+          <t>-2,98; 0,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,66</t>
+          <t>-2,39; 1,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,04</t>
+          <t>-3,41; 0,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 3,66</t>
+          <t>-0,17; 3,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,99</t>
+          <t>-1,27; 2,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,56</t>
+          <t>-0,86; 2,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,66</t>
+          <t>-0,93; 1,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,39</t>
+          <t>-1,36; 1,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,88</t>
+          <t>-1,68; 0,91</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-47,02%</t>
+          <t>-38,66%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-16,65%</t>
+          <t>-11,72%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,41; 32,67</t>
+          <t>-59,04; 33,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,26; 60,87</t>
+          <t>-47,73; 61,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,89; 8,95</t>
+          <t>-67,06; 16,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 191,96</t>
+          <t>-8,12; 179,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,64; 100,92</t>
+          <t>-35,39; 106,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 134,99</t>
+          <t>-24,68; 119,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 65,03</t>
+          <t>-24,47; 59,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,88; 51,77</t>
+          <t>-33,52; 48,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-50,77; 32,36</t>
+          <t>-39,8; 33,09</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,08</t>
+          <t>2,42</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>2,39</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,49</t>
+          <t>-1,68; 2,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,89</t>
+          <t>-2,96; 0,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 4,81</t>
+          <t>0,1; 5,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,43</t>
+          <t>-3,26; 0,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,73</t>
+          <t>-1,46; 3,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 3,38</t>
+          <t>0,16; 4,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,01</t>
+          <t>-1,98; 0,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,09</t>
+          <t>-1,77; 1,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,11</t>
+          <t>0,83; 4,03</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>71,66%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,99; 112,17</t>
+          <t>-39,88; 115,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-69,43; 49,79</t>
+          <t>-69,14; 43,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 207,72</t>
+          <t>-0,16; 238,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-71,99; 21,54</t>
+          <t>-68,52; 38,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 113,98</t>
+          <t>-35,23; 131,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,09; 127,7</t>
+          <t>1,41; 198,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-49,12; 41,78</t>
+          <t>-48,87; 30,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-43,18; 43,22</t>
+          <t>-43,93; 51,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 117,88</t>
+          <t>17,91; 151,48</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,91</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-0,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,49</t>
+          <t>-1,58; 2,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,11</t>
+          <t>-2,36; 1,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,6</t>
+          <t>-2,46; 0,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,73</t>
+          <t>-2,14; 1,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,63</t>
+          <t>-2,93; 0,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,77</t>
+          <t>-1,89; 2,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,29</t>
+          <t>-1,17; 1,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,19</t>
+          <t>-2,16; 0,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 0,85</t>
+          <t>-1,53; 1,09</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-28,97%</t>
+          <t>-24,05%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-5,44%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-14,6%</t>
+          <t>-7,01%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,5; 110,81</t>
+          <t>-40,82; 94,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,94; 48,43</t>
+          <t>-57,91; 48,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 29,08</t>
+          <t>-60,03; 41,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,17; 60,53</t>
+          <t>-42,82; 48,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-59,73; 25,04</t>
+          <t>-59,09; 21,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,82; 57,94</t>
+          <t>-38,39; 66,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 43,21</t>
+          <t>-28,03; 50,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,87; 6,6</t>
+          <t>-50,09; 15,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-45,38; 28,71</t>
+          <t>-34,97; 37,67</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,39</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,86</t>
+          <t>-1,05; 1,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,31</t>
+          <t>-1,54; 0,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,91</t>
+          <t>-0,96; 1,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,09</t>
+          <t>-0,82; 1,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,05</t>
+          <t>-0,88; 0,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,35</t>
+          <t>-0,3; 1,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,73</t>
+          <t>-0,7; 0,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,52</t>
+          <t>-0,97; 0,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,81</t>
+          <t>-0,31; 1,08</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-6,68%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 30,2</t>
+          <t>-26,51; 36,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 11,97</t>
+          <t>-38,13; 13,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,79; 31,03</t>
+          <t>-25,54; 41,22</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 36,2</t>
+          <t>-20,95; 38,28</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 34,3</t>
+          <t>-22,31; 32,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 44,64</t>
+          <t>-7,7; 53,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 24,48</t>
+          <t>-18,16; 21,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 16,3</t>
+          <t>-25,63; 14,4</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 26,05</t>
+          <t>-8,16; 34,74</t>
         </is>
       </c>
     </row>
